--- a/data/trans_dic/P36B02_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36B02_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,83; 96,14</t>
+          <t>91,24; 96,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>89,48; 94,85</t>
+          <t>89,64; 94,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90,64; 95,74</t>
+          <t>90,65; 95,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,05; 91,24</t>
+          <t>84,93; 91,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,69; 98,67</t>
+          <t>94,74; 98,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,8; 97,07</t>
+          <t>92,03; 97,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,05; 96,18</t>
+          <t>90,75; 96,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83,44; 88,94</t>
+          <t>82,69; 88,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>93,66; 96,64</t>
+          <t>93,71; 96,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91,42; 95,46</t>
+          <t>91,55; 95,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91,61; 95,37</t>
+          <t>91,6; 95,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,12; 89,25</t>
+          <t>85,29; 89,19</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,37; 95,1</t>
+          <t>89,57; 95,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,41; 96,81</t>
+          <t>91,4; 96,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,42; 94,7</t>
+          <t>88,74; 94,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,13; 91,98</t>
+          <t>86,68; 92,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,56; 95,71</t>
+          <t>90,41; 95,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,97; 97,56</t>
+          <t>92,89; 97,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,45; 96,3</t>
+          <t>91,28; 96,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>82,95; 88,78</t>
+          <t>82,24; 88,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91,17; 94,91</t>
+          <t>90,86; 94,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93,28; 96,69</t>
+          <t>93,37; 96,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91,06; 94,87</t>
+          <t>91,16; 94,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>85,23; 89,65</t>
+          <t>85,56; 89,72</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,13; 93,89</t>
+          <t>89,16; 93,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,11; 94,87</t>
+          <t>91,04; 94,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86,77; 92,46</t>
+          <t>87,19; 92,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85,69; 97,18</t>
+          <t>83,56; 90,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86,25; 94,78</t>
+          <t>85,85; 94,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,26; 96,88</t>
+          <t>90,78; 96,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,26; 97,39</t>
+          <t>89,92; 97,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83,93; 91,94</t>
+          <t>82,55; 91,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89,29; 93,67</t>
+          <t>89,7; 93,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91,66; 95,03</t>
+          <t>91,66; 94,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88,63; 93,1</t>
+          <t>88,7; 93,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>86,37; 96,03</t>
+          <t>84,75; 89,77</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,36; 93,49</t>
+          <t>90,13; 93,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90,94; 94,11</t>
+          <t>90,7; 94,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,95; 92,45</t>
+          <t>88,81; 92,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,47; 89,75</t>
+          <t>84,78; 89,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,2; 95,93</t>
+          <t>92,48; 95,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,55; 94,66</t>
+          <t>90,64; 94,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,44; 95,57</t>
+          <t>92,41; 95,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>89,63; 96,14</t>
+          <t>88,21; 91,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,55; 93,97</t>
+          <t>91,46; 93,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91,31; 93,79</t>
+          <t>91,24; 93,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90,85; 93,29</t>
+          <t>90,87; 93,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,27; 92,97</t>
+          <t>86,99; 89,92</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,35; 94,89</t>
+          <t>89,15; 94,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90,19; 94,86</t>
+          <t>90,25; 94,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,05; 94,28</t>
+          <t>89,95; 94,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81,01; 88,2</t>
+          <t>81,6; 88,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>91,86; 96,2</t>
+          <t>92,31; 96,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,26; 95,8</t>
+          <t>92,33; 95,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,87; 95,38</t>
+          <t>91,8; 95,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>61,86; 91,87</t>
+          <t>88,58; 92,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>91,92; 95,35</t>
+          <t>91,76; 95,15</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92,29; 95,01</t>
+          <t>92,1; 95,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91,62; 94,34</t>
+          <t>91,62; 94,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,55; 89,47</t>
+          <t>86,68; 90,0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93,99; 98,37</t>
+          <t>94,17; 98,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>94,08; 98,23</t>
+          <t>93,89; 98,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90,64; 96,44</t>
+          <t>90,25; 96,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80,38; 93,81</t>
+          <t>78,68; 92,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92,8; 95,44</t>
+          <t>92,71; 95,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>92,95; 95,79</t>
+          <t>92,81; 95,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,54; 95,49</t>
+          <t>92,57; 95,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>86,83; 91,21</t>
+          <t>86,87; 90,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,41; 95,68</t>
+          <t>93,53; 95,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>93,45; 95,88</t>
+          <t>93,36; 95,86</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92,63; 95,22</t>
+          <t>92,63; 95,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>86,39; 90,72</t>
+          <t>86,41; 90,81</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>91,91; 93,76</t>
+          <t>91,95; 93,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>92,41; 94,17</t>
+          <t>92,29; 94,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90,73; 92,57</t>
+          <t>90,77; 92,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86,8; 90,83</t>
+          <t>86,09; 88,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,46; 95,14</t>
+          <t>93,44; 95,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,28; 94,89</t>
+          <t>93,31; 94,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,19; 94,71</t>
+          <t>93,28; 94,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>81,81; 90,27</t>
+          <t>87,85; 89,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>93,04; 94,21</t>
+          <t>92,87; 94,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93,2; 94,39</t>
+          <t>93,11; 94,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92,2; 93,5</t>
+          <t>92,26; 93,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,23; 89,68</t>
+          <t>87,36; 88,87</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>444697</t>
+          <t>487366</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>385811</t>
+          <t>419975</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>830507</t>
+          <t>907341</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>435055; 455469</t>
+          <t>432265; 454994</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>391196; 414708</t>
+          <t>391915; 413915</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>387973; 409806</t>
+          <t>388009; 409037</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>429693; 460941</t>
+          <t>467622; 501732</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>290403; 302597</t>
+          <t>290535; 302562</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>287848; 304362</t>
+          <t>288565; 304570</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>315999; 333790</t>
+          <t>314955; 333761</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>373359; 397966</t>
+          <t>403876; 432611</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>730962; 754245</t>
+          <t>731349; 754452</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>686361; 716642</t>
+          <t>687338; 715241</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>710085; 739222</t>
+          <t>709980; 739138</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>810955; 850240</t>
+          <t>886225; 926673</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403055</t>
+          <t>433230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>329414</t>
+          <t>362658</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>732469</t>
+          <t>795888</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>327923; 348972</t>
+          <t>328647; 349619</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>382817; 405423</t>
+          <t>382771; 405540</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>330998; 354477</t>
+          <t>332194; 354759</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>389513; 415959</t>
+          <t>418827; 446435</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>336768; 355907</t>
+          <t>336216; 355539</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>314247; 329776</t>
+          <t>313989; 329421</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>338525; 356485</t>
+          <t>337907; 356546</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>317356; 339664</t>
+          <t>347974; 374152</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>673588; 701224</t>
+          <t>671288; 701174</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>705971; 731723</t>
+          <t>706598; 732015</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>677969; 706314</t>
+          <t>678672; 706031</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>711497; 748416</t>
+          <t>775483; 813166</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>612704</t>
+          <t>410913</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>147032</t>
+          <t>164135</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>759736</t>
+          <t>575048</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>482621; 508439</t>
+          <t>482800; 508797</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>573467; 597119</t>
+          <t>573033; 597788</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>452860; 482569</t>
+          <t>455060; 482976</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>572657; 649410</t>
+          <t>394091; 425180</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>144710; 159020</t>
+          <t>144033; 158897</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>236447; 251013</t>
+          <t>235186; 251138</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>149949; 161788</t>
+          <t>149381; 161245</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>140081; 153453</t>
+          <t>154787; 170841</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>633330; 664389</t>
+          <t>636242; 664266</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>814400; 844314</t>
+          <t>814384; 843718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>609813; 640582</t>
+          <t>610309; 642575</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>721366; 802010</t>
+          <t>558592; 591694</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>908797</t>
+          <t>986924</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>903537</t>
+          <t>777689</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1812333</t>
+          <t>1764613</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1119007; 1157747</t>
+          <t>1116172; 1156550</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1054020; 1090797</t>
+          <t>1051206; 1089461</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1021689; 1061850</t>
+          <t>1019986; 1063009</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>884460; 928750</t>
+          <t>959566; 1008590</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>658605; 685244</t>
+          <t>660591; 684975</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>692425; 723870</t>
+          <t>693107; 723688</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>763432; 789301</t>
+          <t>763212; 789081</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>876657; 940378</t>
+          <t>759637; 791982</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1787627; 1834890</t>
+          <t>1785779; 1832302</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1756531; 1804158</t>
+          <t>1755237; 1804898</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1793750; 1841938</t>
+          <t>1794146; 1843950</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1776819; 1871410</t>
+          <t>1733769; 1792225</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>403505</t>
+          <t>484315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>704441</t>
+          <t>751877</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1107946</t>
+          <t>1236192</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>313227; 332656</t>
+          <t>312530; 332275</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>460519; 484365</t>
+          <t>460806; 484465</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>558121; 584355</t>
+          <t>557503; 585605</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>384844; 418983</t>
+          <t>463481; 501395</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>521415; 546042</t>
+          <t>523988; 547179</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>701644; 728578</t>
+          <t>702190; 729287</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>678258; 704149</t>
+          <t>677729; 703635</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>520440; 772963</t>
+          <t>735973; 765273</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>843958; 875498</t>
+          <t>842524; 873666</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1173168; 1207708</t>
+          <t>1170712; 1208053</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1244198; 1281230</t>
+          <t>1244187; 1279372</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>928690; 1177805</t>
+          <t>1212510; 1258934</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211386</t>
+          <t>206605</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>679100</t>
+          <t>753044</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>890486</t>
+          <t>959649</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>280285; 293328</t>
+          <t>280806; 293015</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>250210; 261270</t>
+          <t>249728; 262114</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>259383; 275977</t>
+          <t>258279; 275265</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>193309; 225615</t>
+          <t>186648; 219307</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1158894; 1191868</t>
+          <t>1157766; 1188999</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1030243; 1061613</t>
+          <t>1028640; 1060504</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1000537; 1032368</t>
+          <t>1000831; 1031358</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>661095; 694444</t>
+          <t>733401; 768078</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1444964; 1480069</t>
+          <t>1446863; 1480311</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1284232; 1317619</t>
+          <t>1283077; 1317465</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1266510; 1302000</t>
+          <t>1266601; 1302366</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>865556; 908909</t>
+          <t>934523; 982093</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2984143</t>
+          <t>3009352</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3149334</t>
+          <t>3229378</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6133477</t>
+          <t>6238730</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3004678; 3065145</t>
+          <t>3006056; 3065903</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3161204; 3221625</t>
+          <t>3157370; 3220170</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3065603; 3127841</t>
+          <t>3066873; 3133007</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2930392; 3066317</t>
+          <t>2963720; 3055235</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3156092; 3212732</t>
+          <t>3155321; 3209237</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3306124; 3363015</t>
+          <t>3307129; 3366118</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3288164; 3342049</t>
+          <t>3291589; 3346396</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2927031; 3229751</t>
+          <t>3193757; 3261844</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6183464; 6261729</t>
+          <t>6172175; 6257220</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6491342; 6574638</t>
+          <t>6485092; 6572478</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6368603; 6458358</t>
+          <t>6372788; 6459469</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5926916; 6236481</t>
+          <t>6183303; 6290175</t>
         </is>
       </c>
     </row>
